--- a/results/Int All Data -0.1/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_6_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7564098694057253</v>
+        <v>0.7494566456383422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7581917653430026</v>
+        <v>0.7513126558314178</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7595769585311591</v>
+        <v>0.7516287114572079</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7592205793437037</v>
+        <v>0.7516287114572079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7592205793437037</v>
+        <v>0.7556295296425486</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7606460960935255</v>
+        <v>0.7552731504550931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7696362229032423</v>
+        <v>0.7549974183909682</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7714181188405196</v>
+        <v>0.7549974183909682</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7682107061534206</v>
+        <v>0.7586821809505186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7696362229032423</v>
+        <v>0.758406448886394</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7532024567186262</v>
+        <v>0.7502838418307167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7270527396143175</v>
+        <v>0.7481858902676494</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7260239256136165</v>
+        <v>0.7574778806116206</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7260239256136165</v>
+        <v>0.7525757519781073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7248338173662542</v>
+        <v>0.7572424721091611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7248338173662542</v>
+        <v>0.7572424721091611</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7219424603049452</v>
+        <v>0.7573503770590923</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7219021367432799</v>
+        <v>0.7531947974946227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7215392246882921</v>
+        <v>0.7590243680464384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7215392246882921</v>
+        <v>0.7566506844192461</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7229985321322469</v>
+        <v>0.7643896544608673</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7226421529447914</v>
+        <v>0.7584990353883181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7276652522633007</v>
+        <v>0.7597632578914787</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7292793210863844</v>
+        <v>0.7600389899556035</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7297969945205011</v>
+        <v>0.7514989551917374</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7274974251491071</v>
+        <v>0.7157738564553291</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7274974251491071</v>
+        <v>0.7127277380148913</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7282973635148811</v>
+        <v>0.7089688611995426</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7279409843274256</v>
+        <v>0.7089688611995426</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7279409843274256</v>
+        <v>0.7104347015110297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7279409843274256</v>
+        <v>0.7233787900768895</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7288488276431306</v>
+        <v>0.7233787900768895</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7304694293337466</v>
+        <v>0.7252816566991629</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7257623856410275</v>
+        <v>0.7273730753946979</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7253318921977738</v>
+        <v>0.7210922864405604</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7241417839504115</v>
+        <v>0.7165465369945025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6704702222887022</v>
+        <v>0.7110929442327394</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.672608497413435</v>
+        <v>0.7088805548522086</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6715393598510686</v>
+        <v>0.7143276147464391</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7001771984000331</v>
+        <v>0.7204874330155806</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6937689058933674</v>
+        <v>0.7215227798838141</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6937689058933674</v>
+        <v>0.7019687810029619</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6931030039476542</v>
+        <v>0.7081351321396357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6938222951900974</v>
+        <v>0.715598370117132</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6942931121950164</v>
+        <v>0.7110395549360095</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6919194285678243</v>
+        <v>0.7130100029465485</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.710840189840625</v>
+        <v>0.70956718175699</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7138863082810629</v>
+        <v>0.7110330220684771</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7121785265995839</v>
+        <v>0.7109523749451465</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7036995403564512</v>
+        <v>0.7173672003193445</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7079357670442514</v>
+        <v>0.720372995198117</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7128847521069624</v>
+        <v>0.7152354580621443</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7087629632366259</v>
+        <v>0.7068425254534035</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.705871606175317</v>
+        <v>0.7088936205872733</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7058312826136517</v>
+        <v>0.7101981666520991</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6919324943028889</v>
+        <v>0.7095529896654541</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6881267610583426</v>
+        <v>0.7120814346717752</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6860691330569405</v>
+        <v>0.710265748040365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6672486175100674</v>
+        <v>0.710265748040365</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6667309440759507</v>
+        <v>0.7078330433340873</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6667309440759507</v>
+        <v>0.7050626569577743</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6825760763687709</v>
+        <v>0.7020307306088722</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6814666152447393</v>
+        <v>0.6991666313741639</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6736861952849816</v>
+        <v>0.7008678801881105</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6746343621623521</v>
+        <v>0.706381395114136</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6879882192123975</v>
+        <v>0.7071955255714457</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6935965733532894</v>
+        <v>0.7099997026418916</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6934264935261536</v>
+        <v>0.6999938275665384</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6875358744536044</v>
+        <v>0.705911704465688</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6794589974706539</v>
+        <v>0.6981639488435923</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6794589974706539</v>
+        <v>0.6994684949084182</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6731040942607183</v>
+        <v>0.7056163737989661</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.672909009319924</v>
+        <v>0.7055825831048332</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6694857867329624</v>
+        <v>0.7037135071766929</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6684569727322615</v>
+        <v>0.7030813959251125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6684569727322615</v>
+        <v>0.7088237864860651</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6652223022185618</v>
+        <v>0.7066113971055342</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6775070217062409</v>
+        <v>0.7215531915085338</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6874998310465293</v>
+        <v>0.7080227217638202</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6593501553921388</v>
+        <v>0.7165366250575569</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6593501553921388</v>
+        <v>0.7219095706959893</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6567617882215553</v>
+        <v>0.7304365397247905</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6828952857926802</v>
+        <v>0.7288562615958398</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6828952857926802</v>
+        <v>0.7255540096938744</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6972322267707</v>
+        <v>0.7051847539992413</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6850804173466105</v>
+        <v>0.7055008096250315</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6814763019103907</v>
+        <v>0.7047411948209228</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6867413425988919</v>
+        <v>0.7047411948209228</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6760423077512248</v>
+        <v>0.7056425052690956</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6743138011106775</v>
+        <v>0.7024688832761294</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6793706911233198</v>
+        <v>0.6816540409615299</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6728544936667229</v>
+        <v>0.6748970284914122</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6728544936667229</v>
+        <v>0.6679602495285072</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6616508511200039</v>
+        <v>0.6759618858991884</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5957227288823931</v>
+        <v>0.6823832441409189</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6016547978730786</v>
+        <v>0.6823832441409189</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6163546509060862</v>
+        <v>0.6873049713770294</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6152517226495868</v>
+        <v>0.6869889157512392</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6393460644654356</v>
+        <v>0.6865180987463202</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6317661359575336</v>
+        <v>0.6868744779337757</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6718986675653489</v>
+        <v>0.6740306350938435</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6539226941005052</v>
+        <v>0.6699764276117729</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.653936886192041</v>
+        <v>0.6739499879705129</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6589937762046834</v>
+        <v>0.6739499879705129</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6923377573611901</v>
+        <v>0.6994349294855795</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6909187734789006</v>
+        <v>0.700786331979603</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6903803750857157</v>
+        <v>0.7066093696638862</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6950002387875718</v>
+        <v>0.7116727925440608</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6934940749144194</v>
+        <v>0.7154305430029384</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6928281729687062</v>
+        <v>0.7147581081896928</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.715127553112213</v>
+        <v>0.7147581081896928</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7119266732926464</v>
+        <v>0.714361405440572</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.7130633922432785</v>
+        <v>0.7078920644131728</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6724100334032275</v>
+        <v>0.7042814161094206</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.670345872534293</v>
+        <v>0.7042814161094206</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6699894933468376</v>
+        <v>0.7051892594251257</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6825161542045085</v>
+        <v>0.7050279651784644</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5718505045626447</v>
+        <v>0.7054246679275852</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5703508735570247</v>
+        <v>0.6939245683576731</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5737337725823208</v>
+        <v>0.6912282962371583</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5734177169565308</v>
+        <v>0.6785434949309453</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5485146511944334</v>
+        <v>0.6427942921660557</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4967141929025125</v>
+        <v>0.6410058633612459</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4969899249666373</v>
+        <v>0.6410058633612459</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.504319126524073</v>
+        <v>0.6143961422741407</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5059266624796243</v>
+        <v>0.6167022445130671</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4966673364733148</v>
+        <v>0.6157529512792256</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4968351635875085</v>
+        <v>0.6338848124796692</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4955513424817508</v>
+        <v>0.6101871734129412</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5091428607471978</v>
+        <v>0.6136833838992298</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5054711639227121</v>
+        <v>0.6471330172927257</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5122347092603623</v>
+        <v>0.6483972397958861</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5177689491454559</v>
+        <v>0.5160677003315092</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5100899012680972</v>
+        <v>0.5306869062411863</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5100899012680972</v>
+        <v>0.5413521503947203</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5084355088833482</v>
+        <v>0.538662411141738</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5084355088833482</v>
+        <v>0.5352795121164419</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5182397661503749</v>
+        <v>0.5352795121164419</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5245804772687748</v>
+        <v>0.5312514361045007</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5248965328945649</v>
+        <v>0.5344588487915998</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5248965328945649</v>
+        <v>0.5344588487915998</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5340567395314176</v>
+        <v>0.5356424241714296</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5426240321218844</v>
+        <v>0.5352860449839741</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5430207348710052</v>
+        <v>0.5429051706970704</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5430207348710052</v>
+        <v>0.5401816407499552</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5408552019196718</v>
+        <v>0.5455011970916575</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5408552019196718</v>
+        <v>0.557148398816695</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.528871219609776</v>
+        <v>0.557148398816695</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5126640763471448</v>
+        <v>0.5661461848504153</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5130204555346003</v>
+        <v>0.500591787689915</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5153407498650625</v>
+        <v>0.500591787689915</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5116755859081091</v>
+        <v>0.500591787689915</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5084082510567477</v>
+        <v>0.500591787689915</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5206537733392325</v>
+        <v>0.4999596764383347</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5115634008035878</v>
+        <v>0.4999596764383347</v>
       </c>
     </row>
   </sheetData>
